--- a/ISPEC2026/Registration_Form.xlsx
+++ b/ISPEC2026/Registration_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
-    <t>Registration form for 2025 International Conference on Information Security Practice and Experience (ISPEC 2025)</t>
+    <t>Registration form for 2026 International Conference on Information Security Practice and Experience (ISPEC 2026)</t>
   </si>
   <si>
     <t>No.</t>
@@ -97,9 +97,55 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Standard (Before 16 October)：4000CNY；
-Standard (After 16 October)：4500CNY；
+    <r>
+      <t>Standard (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Before 16 October</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：4000CNY；
+Standard (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>After 16 October</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)：4500CNY；
 </t>
+    </r>
   </si>
   <si>
     <t>Please specify who will present the paper  at the conference in the column of "Report Person".</t>
@@ -124,7 +170,16 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>Please email to 1841974993@qq.com</t>
+      <t xml:space="preserve">Please email to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1841974993@qq.com</t>
     </r>
   </si>
   <si>
@@ -168,7 +223,16 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：1841974993@qq.com</t>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1841974993@qq.com</t>
     </r>
   </si>
 </sst>
@@ -183,7 +247,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +288,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -262,12 +332,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -409,6 +473,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -945,12 +1037,15 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -959,32 +1054,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1319,7 +1411,7 @@
     <col min="16374" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="81" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="81" customHeight="1" spans="1:13">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1331,7 +1423,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+    <row r="2" s="2" customFormat="1" ht="28.5" customHeight="1" spans="1:13">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1357,7 +1449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+    <row r="3" s="2" customFormat="1" ht="28.5" customHeight="1" spans="1:13">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1367,7 +1459,7 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="45" customHeight="1" spans="1:8">
+    <row r="4" s="3" customFormat="1" ht="45" customHeight="1" spans="1:13">
       <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
@@ -1383,7 +1475,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="9"/>
     </row>
-    <row r="5" s="3" customFormat="1" ht="45" customHeight="1" spans="1:8">
+    <row r="5" s="3" customFormat="1" ht="45" customHeight="1" spans="1:13">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -1414,13 +1506,13 @@
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="45" customHeight="1" spans="1:8">
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="45" customHeight="1" spans="1:13">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -1436,7 +1528,7 @@
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="45" customHeight="1" spans="1:8">
+    <row r="8" s="3" customFormat="1" ht="45" customHeight="1" spans="1:13">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
@@ -1452,151 +1544,151 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14" t="s">
+    <row r="9" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="14"/>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="23.25" customHeight="1" spans="1:7">
-      <c r="A10" s="13"/>
-      <c r="B10" s="15" t="s">
+      <c r="C9" s="15"/>
+    </row>
+    <row r="10" s="4" customFormat="1" ht="23.25" customHeight="1" spans="1:13">
+      <c r="A10" s="14"/>
+      <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A11" s="13"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="55.5" customHeight="1" spans="1:7">
-      <c r="A12" s="13"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" s="4" customFormat="1" spans="1:10">
-      <c r="A13" s="13"/>
-      <c r="B13" s="17" t="s">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" s="4" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
+      <c r="A11" s="14"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" s="4" customFormat="1" ht="55.5" customHeight="1" spans="1:13">
+      <c r="A12" s="14"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:13">
+      <c r="A13" s="14"/>
+      <c r="B13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" s="4" customFormat="1" spans="1:10">
-      <c r="A14" s="13"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" s="4" customFormat="1" spans="1:8">
-      <c r="A15" s="13"/>
-      <c r="B15" s="18" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:13">
+      <c r="A14" s="14"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="1:13">
+      <c r="A15" s="14"/>
+      <c r="B15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" s="4" customFormat="1" spans="1:8">
-      <c r="A16" s="13"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" s="4" customFormat="1" spans="1:8">
-      <c r="A17" s="13"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" s="4" customFormat="1" spans="1:13">
+      <c r="A16" s="14"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" s="4" customFormat="1" spans="1:17 16374:16383">
+      <c r="A17" s="14"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:17 16374:16383">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A19" s="13"/>
-      <c r="B19" s="20" t="s">
+      <c r="C18" s="15"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:17 16374:16383">
+      <c r="A19" s="14"/>
+      <c r="B19" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="26"/>
-    </row>
-    <row r="20" s="4" customFormat="1" spans="1:10">
-      <c r="A20" s="13"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="5:6">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24"/>
+    </row>
+    <row r="20" s="4" customFormat="1" spans="1:17 16374:16383">
+      <c r="A20" s="14"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:17 16374:16383">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" s="1" customFormat="1"/>
-    <row r="24" s="1" customFormat="1" spans="5:16383">
+    <row r="24" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="XET24" s="4"/>
@@ -1610,7 +1702,7 @@
       <c r="XFB24" s="4"/>
       <c r="XFC24" s="4"/>
     </row>
-    <row r="25" s="1" customFormat="1" spans="5:16383">
+    <row r="25" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="XET25" s="4"/>
@@ -1624,7 +1716,7 @@
       <c r="XFB25" s="4"/>
       <c r="XFC25" s="4"/>
     </row>
-    <row r="26" s="1" customFormat="1" spans="5:16383">
+    <row r="26" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="XET26" s="4"/>
@@ -1638,7 +1730,7 @@
       <c r="XFB26" s="4"/>
       <c r="XFC26" s="4"/>
     </row>
-    <row r="27" s="1" customFormat="1" spans="5:16383">
+    <row r="27" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="XET27" s="4"/>
@@ -1652,7 +1744,7 @@
       <c r="XFB27" s="4"/>
       <c r="XFC27" s="4"/>
     </row>
-    <row r="28" s="1" customFormat="1" spans="5:16383">
+    <row r="28" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="XET28" s="4"/>
@@ -1666,7 +1758,7 @@
       <c r="XFB28" s="4"/>
       <c r="XFC28" s="4"/>
     </row>
-    <row r="29" s="1" customFormat="1" spans="5:16383">
+    <row r="29" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="XET29" s="4"/>
@@ -1680,7 +1772,7 @@
       <c r="XFB29" s="4"/>
       <c r="XFC29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" spans="5:16383">
+    <row r="30" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="XET30" s="4"/>
@@ -1694,7 +1786,7 @@
       <c r="XFB30" s="4"/>
       <c r="XFC30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" spans="5:16383">
+    <row r="31" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="XET31" s="4"/>
@@ -1708,17 +1800,17 @@
       <c r="XFB31" s="4"/>
       <c r="XFC31" s="4"/>
     </row>
-    <row r="32" s="1" customFormat="1" spans="5:16383">
+    <row r="32" s="1" customFormat="1" spans="1:17 16374:16383">
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-      <c r="J32" s="14"/>
+      <c r="J32" s="15"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="24"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="21"/>
       <c r="XET32" s="4"/>
       <c r="XEU32" s="4"/>
       <c r="XEV32" s="4"/>
@@ -1730,17 +1822,17 @@
       <c r="XFB32" s="4"/>
       <c r="XFC32" s="4"/>
     </row>
-    <row r="33" s="1" customFormat="1" spans="5:16383">
+    <row r="33" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="28"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="27"/>
       <c r="XET33" s="4"/>
       <c r="XEU33" s="4"/>
       <c r="XEV33" s="4"/>
@@ -1752,17 +1844,17 @@
       <c r="XFB33" s="4"/>
       <c r="XFC33" s="4"/>
     </row>
-    <row r="34" s="1" customFormat="1" spans="5:16383">
+    <row r="34" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="28"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="27"/>
       <c r="XET34" s="4"/>
       <c r="XEU34" s="4"/>
       <c r="XEV34" s="4"/>
@@ -1774,17 +1866,17 @@
       <c r="XFB34" s="4"/>
       <c r="XFC34" s="4"/>
     </row>
-    <row r="35" s="1" customFormat="1" spans="5:16383">
+    <row r="35" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="27"/>
       <c r="XET35" s="4"/>
       <c r="XEU35" s="4"/>
       <c r="XEV35" s="4"/>
@@ -1796,17 +1888,17 @@
       <c r="XFB35" s="4"/>
       <c r="XFC35" s="4"/>
     </row>
-    <row r="36" s="1" customFormat="1" spans="5:16383">
+    <row r="36" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
       <c r="XET36" s="4"/>
       <c r="XEU36" s="4"/>
       <c r="XEV36" s="4"/>
@@ -1818,17 +1910,17 @@
       <c r="XFB36" s="4"/>
       <c r="XFC36" s="4"/>
     </row>
-    <row r="37" s="1" customFormat="1" spans="5:16383">
+    <row r="37" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
       <c r="XET37" s="4"/>
       <c r="XEU37" s="4"/>
       <c r="XEV37" s="4"/>
@@ -1840,17 +1932,17 @@
       <c r="XFB37" s="4"/>
       <c r="XFC37" s="4"/>
     </row>
-    <row r="38" s="1" customFormat="1" spans="5:16383">
+    <row r="38" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
       <c r="XET38" s="4"/>
       <c r="XEU38" s="4"/>
       <c r="XEV38" s="4"/>
@@ -1862,17 +1954,17 @@
       <c r="XFB38" s="4"/>
       <c r="XFC38" s="4"/>
     </row>
-    <row r="39" s="1" customFormat="1" spans="5:16383">
+    <row r="39" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
       <c r="XET39" s="4"/>
       <c r="XEU39" s="4"/>
       <c r="XEV39" s="4"/>
@@ -1884,17 +1976,17 @@
       <c r="XFB39" s="4"/>
       <c r="XFC39" s="4"/>
     </row>
-    <row r="40" s="1" customFormat="1" spans="5:16383">
+    <row r="40" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
       <c r="XET40" s="4"/>
       <c r="XEU40" s="4"/>
       <c r="XEV40" s="4"/>
@@ -1906,17 +1998,17 @@
       <c r="XFB40" s="4"/>
       <c r="XFC40" s="4"/>
     </row>
-    <row r="41" s="1" customFormat="1" spans="5:16383">
+    <row r="41" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
       <c r="XET41" s="4"/>
       <c r="XEU41" s="4"/>
       <c r="XEV41" s="4"/>
@@ -1928,17 +2020,17 @@
       <c r="XFB41" s="4"/>
       <c r="XFC41" s="4"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="5:16383">
+    <row r="42" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
       <c r="XET42" s="4"/>
       <c r="XEU42" s="4"/>
       <c r="XEV42" s="4"/>
@@ -1950,17 +2042,17 @@
       <c r="XFB42" s="4"/>
       <c r="XFC42" s="4"/>
     </row>
-    <row r="43" s="1" customFormat="1" spans="5:16383">
+    <row r="43" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
       <c r="XET43" s="4"/>
       <c r="XEU43" s="4"/>
       <c r="XEV43" s="4"/>
@@ -1972,17 +2064,17 @@
       <c r="XFB43" s="4"/>
       <c r="XFC43" s="4"/>
     </row>
-    <row r="44" s="1" customFormat="1" spans="5:16383">
+    <row r="44" s="1" customFormat="1" spans="5:17 16374:16383">
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="27"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
       <c r="XET44" s="4"/>
       <c r="XEU44" s="4"/>
       <c r="XEV44" s="4"/>
